--- a/PH0__Allowables_and_Failure_Scenarios/Static_TEST__Data-Processing_UPDATED/weibull_plots/weibull_fit_summary.xlsx
+++ b/PH0__Allowables_and_Failure_Scenarios/Static_TEST__Data-Processing_UPDATED/weibull_plots/weibull_fit_summary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Temp\weibull_plots\weibull_batch_A.png</t>
+          <t>weibull_plots\weibull_batch_A.png</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C:\Temp\weibull_plots\weibull_batch_B.png</t>
+          <t>weibull_plots\weibull_batch_B.png</t>
         </is>
       </c>
     </row>
